--- a/AAII_Financials/Quarterly/GRIN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GRIN_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="92">
   <si>
     <t>GRIN</t>
   </si>
@@ -656,93 +656,94 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="26" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44834</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44742</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44651</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44561</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44469</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44377</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44286</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44196</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44012</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>43830</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>43646</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43281</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>42916</v>
       </c>
-      <c r="T7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U7" s="2" t="s">
         <v>3</v>
       </c>
@@ -758,62 +759,65 @@
       <c r="Y7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>112500</v>
+      </c>
+      <c r="E8" s="3">
         <v>109100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>76800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>81400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>107200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>161600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>110300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>89500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>135100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>178300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>68400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>112100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>167100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>163800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>167200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>150800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>194100</v>
       </c>
-      <c r="T8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U8" s="3" t="s">
         <v>3</v>
       </c>
@@ -829,62 +833,65 @@
       <c r="Y8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>108300</v>
+      </c>
+      <c r="E9" s="3">
         <v>92600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>69800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>58400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>68700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>97000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>69600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>22700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>73200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>132900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>55800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>105900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>158200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>149200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>161300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>148400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>184300</v>
       </c>
-      <c r="T9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U9" s="3" t="s">
         <v>3</v>
       </c>
@@ -900,62 +907,65 @@
       <c r="Y9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E10" s="3">
         <v>16500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>7000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>23000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>38500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>64600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>40700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>66800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>61900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>45400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>12600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>6200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>8900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>14600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>5900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>2400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>9800</v>
       </c>
-      <c r="T10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U10" s="3" t="s">
         <v>3</v>
       </c>
@@ -971,8 +981,11 @@
       <c r="Y10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -998,8 +1011,9 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1069,8 +1083,11 @@
       <c r="Y12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1140,8 +1157,11 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1175,17 +1195,17 @@
       <c r="M14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N14" s="3">
+      <c r="N14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O14" s="3">
         <v>14600</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>4200</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="3" t="s">
-        <v>3</v>
+      <c r="Q14" s="3">
+        <v>0</v>
       </c>
       <c r="R14" s="3" t="s">
         <v>3</v>
@@ -1202,8 +1222,8 @@
       <c r="V14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
+      <c r="W14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X14" s="3">
         <v>0</v>
@@ -1211,8 +1231,11 @@
       <c r="Y14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1246,18 +1269,18 @@
       <c r="M15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N15" s="3">
+      <c r="N15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O15" s="3">
         <v>600</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>400</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>600</v>
       </c>
-      <c r="Q15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1270,8 +1293,8 @@
       <c r="U15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V15" s="3">
-        <v>0</v>
+      <c r="V15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W15" s="3">
         <v>0</v>
@@ -1282,8 +1305,11 @@
       <c r="Y15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1306,62 +1332,63 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>120900</v>
+      </c>
+      <c r="E17" s="3">
         <v>103300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>81000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>85600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>85000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>104700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>81100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>31200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>85800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>147900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>65300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>140600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>179000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>188300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>185500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>162100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>199100</v>
       </c>
-      <c r="T17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1377,62 +1404,65 @@
       <c r="Y17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-8400</v>
+      </c>
+      <c r="E18" s="3">
         <v>5800</v>
-      </c>
-      <c r="E18" s="3">
-        <v>-4200</v>
       </c>
       <c r="F18" s="3">
         <v>-4200</v>
       </c>
       <c r="G18" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="H18" s="3">
         <v>22200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>56900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>29200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>58300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>49300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>30400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>3100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-28500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-11900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-24500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-18300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-11300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-5000</v>
       </c>
-      <c r="T18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1448,8 +1478,11 @@
       <c r="Y18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1475,8 +1508,9 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1528,8 +1562,8 @@
       <c r="S20" s="3">
         <v>0</v>
       </c>
-      <c r="T20" s="3" t="s">
-        <v>3</v>
+      <c r="T20" s="3">
+        <v>0</v>
       </c>
       <c r="U20" s="3" t="s">
         <v>3</v>
@@ -1546,62 +1580,65 @@
       <c r="Y20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E21" s="3">
         <v>20400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>11500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>13000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>38800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>73200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>46400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>74200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>65100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>60600</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N21" s="3">
+      <c r="N21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O21" s="3">
         <v>23000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-34900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>24300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-10000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-4500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>5100</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1617,8 +1654,11 @@
       <c r="Y21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1688,62 +1728,65 @@
       <c r="Y22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-8400</v>
+      </c>
+      <c r="E23" s="3">
         <v>5800</v>
-      </c>
-      <c r="E23" s="3">
-        <v>-4200</v>
       </c>
       <c r="F23" s="3">
         <v>-4200</v>
       </c>
       <c r="G23" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="H23" s="3">
         <v>22200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>56900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>29200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>58200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>49300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>30400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>3200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-28500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-11900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-24500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-18300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-11300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-5100</v>
       </c>
-      <c r="T23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1759,62 +1802,65 @@
       <c r="Y23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3">
         <v>200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>2300</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
       <c r="L24" s="3">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3">
         <v>-100</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
-      </c>
       <c r="N24" s="3">
+        <v>0</v>
+      </c>
+      <c r="O24" s="3">
         <v>300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>2100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>1900</v>
       </c>
-      <c r="T24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1830,8 +1876,11 @@
       <c r="Y24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1901,62 +1950,65 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-8500</v>
+      </c>
+      <c r="E26" s="3">
         <v>5500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-4300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-4600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>22200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>56800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>29000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>56000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>49300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>30400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>3200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-28800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-12300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-24500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-19000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-13500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-7000</v>
       </c>
-      <c r="T26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1972,62 +2024,65 @@
       <c r="Y26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-8500</v>
+      </c>
+      <c r="E27" s="3">
         <v>5500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-4300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-4600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>22200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>56800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>29000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>56000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>44200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>19900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>2200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-28300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-10500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-24500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-19000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-13500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-7000</v>
       </c>
-      <c r="T27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2043,8 +2098,11 @@
       <c r="Y27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2114,8 +2172,11 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2125,41 +2186,41 @@
       <c r="E29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F29" s="3">
-        <v>0</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H29" s="3">
-        <v>0</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J29" s="3">
+      <c r="F29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K29" s="3">
         <v>-3200</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>-200</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>-2800</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>200</v>
       </c>
-      <c r="N29" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O29" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q29" s="3">
-        <v>0</v>
+      <c r="Q29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R29" s="3">
         <v>0</v>
@@ -2185,8 +2246,11 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2256,8 +2320,11 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2327,8 +2394,11 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2380,8 +2450,8 @@
       <c r="S32" s="3">
         <v>0</v>
       </c>
-      <c r="T32" s="3" t="s">
-        <v>3</v>
+      <c r="T32" s="3">
+        <v>0</v>
       </c>
       <c r="U32" s="3" t="s">
         <v>3</v>
@@ -2398,62 +2468,65 @@
       <c r="Y32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-8500</v>
+      </c>
+      <c r="E33" s="3">
         <v>5500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-4300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-4600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>22200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>56800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>29000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>52800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>44000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>17000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>2400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-28300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-10500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-24500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-19000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-13500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-7000</v>
       </c>
-      <c r="T33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2469,8 +2542,11 @@
       <c r="Y33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2540,62 +2616,65 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-8500</v>
+      </c>
+      <c r="E35" s="3">
         <v>5500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-4300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-4600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>22200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>56800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>29000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>52800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>44000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>17000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>2400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-28300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-10500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-24500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-19000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-13500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-7000</v>
       </c>
-      <c r="T35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2611,67 +2690,70 @@
       <c r="Y35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44834</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44742</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44651</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44561</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44469</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44377</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44286</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44196</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44012</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>43830</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>43646</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43281</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>42916</v>
       </c>
-      <c r="T38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2687,8 +2769,11 @@
       <c r="Y38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2714,8 +2799,9 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2741,59 +2827,60 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>71400</v>
+      </c>
+      <c r="E41" s="3">
         <v>85900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>51800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>52200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>146300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>165400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>106500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>107100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>78500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>60700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>41300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>44700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>35600</v>
-      </c>
-      <c r="P41" s="3">
-        <v>37900</v>
       </c>
       <c r="Q41" s="3">
         <v>37900</v>
       </c>
       <c r="R41" s="3">
+        <v>37900</v>
+      </c>
+      <c r="S41" s="3">
         <v>54100</v>
       </c>
-      <c r="S41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2803,17 +2890,20 @@
       <c r="V41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W41" s="3">
-        <v>0</v>
+      <c r="W41" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X41" s="3">
         <v>0</v>
       </c>
-      <c r="Y41" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Y41" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2883,59 +2973,62 @@
       <c r="Y42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>24500</v>
+      </c>
+      <c r="E43" s="3">
         <v>24900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>28600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>37700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>37000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>41300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>38600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>35100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>34400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>31000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>28400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>39200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>38900</v>
-      </c>
-      <c r="P43" s="3">
-        <v>45500</v>
       </c>
       <c r="Q43" s="3">
         <v>45500</v>
       </c>
       <c r="R43" s="3">
+        <v>45500</v>
+      </c>
+      <c r="S43" s="3">
         <v>72700</v>
       </c>
-      <c r="S43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2945,68 +3038,71 @@
       <c r="V43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W43" s="3">
-        <v>0</v>
+      <c r="W43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X43" s="3">
         <v>0</v>
       </c>
-      <c r="Y43" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Y43" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>11500</v>
+      </c>
+      <c r="E44" s="3">
         <v>12500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>10900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>15300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>18100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>20100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>16800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>13900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>12600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>12700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>8700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>7800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>12200</v>
-      </c>
-      <c r="P44" s="3">
-        <v>8600</v>
       </c>
       <c r="Q44" s="3">
         <v>8600</v>
       </c>
       <c r="R44" s="3">
+        <v>8600</v>
+      </c>
+      <c r="S44" s="3">
         <v>10900</v>
       </c>
-      <c r="S44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3016,68 +3112,71 @@
       <c r="V44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W44" s="3">
-        <v>0</v>
+      <c r="W44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X44" s="3">
         <v>0</v>
       </c>
-      <c r="Y44" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Y44" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>400</v>
+      </c>
+      <c r="E45" s="3">
         <v>100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>2400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>2700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>10600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>5400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>5800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>4300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>3800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>4900</v>
-      </c>
-      <c r="P45" s="3">
-        <v>700</v>
       </c>
       <c r="Q45" s="3">
         <v>700</v>
       </c>
       <c r="R45" s="3">
+        <v>700</v>
+      </c>
+      <c r="S45" s="3">
         <v>1100</v>
       </c>
-      <c r="S45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3087,68 +3186,71 @@
       <c r="V45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W45" s="3">
-        <v>0</v>
+      <c r="W45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X45" s="3">
         <v>0</v>
       </c>
-      <c r="Y45" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Y45" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>107700</v>
+      </c>
+      <c r="E46" s="3">
         <v>123400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>91500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>105200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>203700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>229400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>172500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>161500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>131300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>106800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>82600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>95600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>91500</v>
-      </c>
-      <c r="P46" s="3">
-        <v>92700</v>
       </c>
       <c r="Q46" s="3">
         <v>92700</v>
       </c>
       <c r="R46" s="3">
+        <v>92700</v>
+      </c>
+      <c r="S46" s="3">
         <v>138900</v>
       </c>
-      <c r="S46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3158,68 +3260,71 @@
       <c r="V46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W46" s="3">
-        <v>0</v>
+      <c r="W46" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X46" s="3">
         <v>0</v>
       </c>
-      <c r="Y46" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Y46" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E47" s="3">
         <v>6500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>6400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>4600</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>5500</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>5000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>5500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>4100</v>
-      </c>
-      <c r="K47" s="3">
-        <v>3200</v>
       </c>
       <c r="L47" s="3">
         <v>3200</v>
       </c>
       <c r="M47" s="3">
+        <v>3200</v>
+      </c>
+      <c r="N47" s="3">
         <v>3300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>3900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>55100</v>
-      </c>
-      <c r="P47" s="3">
-        <v>52100</v>
       </c>
       <c r="Q47" s="3">
         <v>52100</v>
       </c>
       <c r="R47" s="3">
+        <v>52100</v>
+      </c>
+      <c r="S47" s="3">
         <v>65300</v>
       </c>
-      <c r="S47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3229,68 +3334,71 @@
       <c r="V47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W47" s="3">
-        <v>0</v>
+      <c r="W47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X47" s="3">
         <v>0</v>
       </c>
-      <c r="Y47" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Y47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>353400</v>
+      </c>
+      <c r="E48" s="3">
         <v>373200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>406700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>433600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>436200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>443800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>470100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>469900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>483600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>465900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>524400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>538600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>360400</v>
-      </c>
-      <c r="P48" s="3">
-        <v>355400</v>
       </c>
       <c r="Q48" s="3">
         <v>355400</v>
       </c>
       <c r="R48" s="3">
+        <v>355400</v>
+      </c>
+      <c r="S48" s="3">
         <v>262400</v>
       </c>
-      <c r="S48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3300,22 +3408,25 @@
       <c r="V48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W48" s="3">
-        <v>0</v>
+      <c r="W48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X48" s="3">
         <v>0</v>
       </c>
-      <c r="Y48" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Y48" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E49" s="3">
         <v>200</v>
@@ -3336,32 +3447,32 @@
         <v>200</v>
       </c>
       <c r="K49" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="L49" s="3">
         <v>300</v>
       </c>
       <c r="M49" s="3">
+        <v>300</v>
+      </c>
+      <c r="N49" s="3">
         <v>1400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1100</v>
-      </c>
-      <c r="P49" s="3">
-        <v>7600</v>
       </c>
       <c r="Q49" s="3">
         <v>7600</v>
       </c>
       <c r="R49" s="3">
+        <v>7600</v>
+      </c>
+      <c r="S49" s="3">
         <v>7700</v>
       </c>
-      <c r="S49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3371,17 +3482,20 @@
       <c r="V49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W49" s="3">
-        <v>0</v>
+      <c r="W49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X49" s="3">
         <v>0</v>
       </c>
-      <c r="Y49" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Y49" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3451,8 +3565,11 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3522,8 +3639,11 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3531,50 +3651,50 @@
         <v>5400</v>
       </c>
       <c r="E52" s="3">
-        <v>5600</v>
+        <v>5400</v>
       </c>
       <c r="F52" s="3">
         <v>5600</v>
       </c>
       <c r="G52" s="3">
+        <v>5600</v>
+      </c>
+      <c r="H52" s="3">
         <v>6000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>6400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>8300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>9400</v>
-      </c>
-      <c r="K52" s="3">
-        <v>8600</v>
       </c>
       <c r="L52" s="3">
         <v>8600</v>
       </c>
       <c r="M52" s="3">
+        <v>8600</v>
+      </c>
+      <c r="N52" s="3">
         <v>10400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>11700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>10900</v>
-      </c>
-      <c r="P52" s="3">
-        <v>14200</v>
       </c>
       <c r="Q52" s="3">
         <v>14200</v>
       </c>
       <c r="R52" s="3">
+        <v>14200</v>
+      </c>
+      <c r="S52" s="3">
         <v>1000</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3584,17 +3704,20 @@
       <c r="V52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W52" s="3">
-        <v>0</v>
+      <c r="W52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X52" s="3">
         <v>0</v>
       </c>
-      <c r="Y52" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Y52" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3664,59 +3787,62 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>471800</v>
+      </c>
+      <c r="E54" s="3">
         <v>508700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>510400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>549200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>651700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>684800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>656700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>645200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>627000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>584900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>622100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>651000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>519100</v>
-      </c>
-      <c r="P54" s="3">
-        <v>521900</v>
       </c>
       <c r="Q54" s="3">
         <v>521900</v>
       </c>
       <c r="R54" s="3">
+        <v>521900</v>
+      </c>
+      <c r="S54" s="3">
         <v>475300</v>
       </c>
-      <c r="S54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3726,17 +3852,20 @@
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W54" s="3">
-        <v>0</v>
+      <c r="W54" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X54" s="3">
         <v>0</v>
       </c>
-      <c r="Y54" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Y54" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3762,8 +3891,9 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3789,59 +3919,60 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>17600</v>
+      </c>
+      <c r="E57" s="3">
         <v>15000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>17700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>29600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>28000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>27700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>24400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>33900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>31500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>29200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>27400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>24100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>28300</v>
-      </c>
-      <c r="P57" s="3">
-        <v>27200</v>
       </c>
       <c r="Q57" s="3">
         <v>27200</v>
       </c>
       <c r="R57" s="3">
+        <v>27200</v>
+      </c>
+      <c r="S57" s="3">
         <v>20400</v>
       </c>
-      <c r="S57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3851,68 +3982,71 @@
       <c r="V57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W57" s="3">
-        <v>0</v>
+      <c r="W57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X57" s="3">
         <v>0</v>
       </c>
-      <c r="Y57" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Y57" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>39100</v>
+      </c>
+      <c r="E58" s="3">
         <v>56500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>48500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>55400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>55700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>76600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>65900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>55400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>60200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>55700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>81500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>101600</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>45000</v>
-      </c>
-      <c r="P58" s="3">
-        <v>46100</v>
       </c>
       <c r="Q58" s="3">
         <v>46100</v>
       </c>
       <c r="R58" s="3">
+        <v>46100</v>
+      </c>
+      <c r="S58" s="3">
         <v>19200</v>
       </c>
-      <c r="S58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3922,68 +4056,71 @@
       <c r="V58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W58" s="3">
-        <v>0</v>
+      <c r="W58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X58" s="3">
         <v>0</v>
       </c>
-      <c r="Y58" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Y58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E59" s="3">
         <v>3900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>4000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>5700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>6900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>15000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>7400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>11100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>10100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>13300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>9000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>9400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>13500</v>
-      </c>
-      <c r="P59" s="3">
-        <v>15400</v>
       </c>
       <c r="Q59" s="3">
         <v>15400</v>
       </c>
       <c r="R59" s="3">
+        <v>15400</v>
+      </c>
+      <c r="S59" s="3">
         <v>22800</v>
       </c>
-      <c r="S59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3993,68 +4130,71 @@
       <c r="V59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W59" s="3">
-        <v>0</v>
+      <c r="W59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X59" s="3">
         <v>0</v>
       </c>
-      <c r="Y59" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Y59" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>61100</v>
+      </c>
+      <c r="E60" s="3">
         <v>75400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>70300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>90700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>90600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>119300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>97700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>100300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>101800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>98100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>117900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>135100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>86800</v>
-      </c>
-      <c r="P60" s="3">
-        <v>88700</v>
       </c>
       <c r="Q60" s="3">
         <v>88700</v>
       </c>
       <c r="R60" s="3">
+        <v>88700</v>
+      </c>
+      <c r="S60" s="3">
         <v>62400</v>
       </c>
-      <c r="S60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4064,68 +4204,71 @@
       <c r="V60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W60" s="3">
-        <v>0</v>
+      <c r="W60" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X60" s="3">
         <v>0</v>
       </c>
-      <c r="Y60" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Y60" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>129800</v>
+      </c>
+      <c r="E61" s="3">
         <v>144400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>156200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>169700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>170100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>176200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>214800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>223500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>234000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>200600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>248200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>238300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>178200</v>
-      </c>
-      <c r="P61" s="3">
-        <v>154200</v>
       </c>
       <c r="Q61" s="3">
         <v>154200</v>
       </c>
       <c r="R61" s="3">
+        <v>154200</v>
+      </c>
+      <c r="S61" s="3">
         <v>108100</v>
       </c>
-      <c r="S61" s="3">
-        <v>0</v>
-      </c>
       <c r="T61" s="3">
         <v>0</v>
       </c>
@@ -4144,8 +4287,11 @@
       <c r="Y61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4153,50 +4299,50 @@
         <v>1100</v>
       </c>
       <c r="E62" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F62" s="3">
         <v>1200</v>
-      </c>
-      <c r="F62" s="3">
-        <v>1400</v>
       </c>
       <c r="G62" s="3">
         <v>1400</v>
       </c>
       <c r="H62" s="3">
+        <v>1400</v>
+      </c>
+      <c r="I62" s="3">
         <v>1800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>2100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2300</v>
-      </c>
-      <c r="L62" s="3">
-        <v>2000</v>
       </c>
       <c r="M62" s="3">
         <v>2000</v>
       </c>
       <c r="N62" s="3">
+        <v>2000</v>
+      </c>
+      <c r="O62" s="3">
         <v>1700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2100</v>
-      </c>
-      <c r="P62" s="3">
-        <v>2300</v>
       </c>
       <c r="Q62" s="3">
         <v>2300</v>
       </c>
       <c r="R62" s="3">
+        <v>2300</v>
+      </c>
+      <c r="S62" s="3">
         <v>2500</v>
       </c>
-      <c r="S62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4206,17 +4352,20 @@
       <c r="V62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W62" s="3">
-        <v>0</v>
+      <c r="W62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X62" s="3">
         <v>0</v>
       </c>
-      <c r="Y62" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Y62" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4286,8 +4435,11 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4357,8 +4509,11 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4428,59 +4583,62 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>192000</v>
+      </c>
+      <c r="E66" s="3">
         <v>220900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>227700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>261800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>262100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>297400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>314500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>325500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>338100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>347900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>409900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>417400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>267100</v>
-      </c>
-      <c r="P66" s="3">
-        <v>245200</v>
       </c>
       <c r="Q66" s="3">
         <v>245200</v>
       </c>
       <c r="R66" s="3">
+        <v>245200</v>
+      </c>
+      <c r="S66" s="3">
         <v>172900</v>
       </c>
-      <c r="S66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4490,17 +4648,20 @@
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W66" s="3">
-        <v>0</v>
+      <c r="W66" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X66" s="3">
         <v>0</v>
       </c>
-      <c r="Y66" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Y66" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4526,8 +4687,9 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4597,8 +4759,11 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4668,8 +4833,11 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4739,8 +4907,11 @@
       <c r="Y70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4810,59 +4981,62 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-40900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-32900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-38000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-21200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>68800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>73100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>21500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>15100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-31700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-77500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-99800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-75500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-64400</v>
-      </c>
-      <c r="P72" s="3">
-        <v>-43900</v>
       </c>
       <c r="Q72" s="3">
         <v>-43900</v>
       </c>
       <c r="R72" s="3">
+        <v>-43900</v>
+      </c>
+      <c r="S72" s="3">
         <v>-19600</v>
       </c>
-      <c r="S72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4872,17 +5046,20 @@
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W72" s="3">
-        <v>0</v>
+      <c r="W72" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X72" s="3">
         <v>0</v>
       </c>
-      <c r="Y72" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Y72" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4952,8 +5129,11 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5023,8 +5203,11 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5094,59 +5277,62 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>279800</v>
+      </c>
+      <c r="E76" s="3">
         <v>287800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>282700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>287400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>389500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>387500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>342100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>319600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>289000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>236900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>212200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>233600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>251900</v>
-      </c>
-      <c r="P76" s="3">
-        <v>276700</v>
       </c>
       <c r="Q76" s="3">
         <v>276700</v>
       </c>
       <c r="R76" s="3">
+        <v>276700</v>
+      </c>
+      <c r="S76" s="3">
         <v>302400</v>
       </c>
-      <c r="S76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5156,17 +5342,20 @@
       <c r="V76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W76" s="3">
-        <v>0</v>
+      <c r="W76" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X76" s="3">
         <v>0</v>
       </c>
-      <c r="Y76" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Y76" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5236,67 +5425,70 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44834</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44742</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44651</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44561</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44469</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44377</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44286</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44196</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44012</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>43830</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>43646</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43281</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>42916</v>
       </c>
-      <c r="T80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U80" s="2" t="s">
         <v>3</v>
       </c>
@@ -5312,62 +5504,65 @@
       <c r="Y80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-8500</v>
+      </c>
+      <c r="E81" s="3">
         <v>5500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-4300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-4600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>22200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>56800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>29000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>52800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>44000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>17000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>2400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-28300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-10500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-24500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-19000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-13500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-7000</v>
       </c>
-      <c r="T81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U81" s="3" t="s">
         <v>3</v>
       </c>
@@ -5383,8 +5578,11 @@
       <c r="Y81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5410,62 +5608,63 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>14000</v>
+      </c>
+      <c r="E83" s="3">
         <v>14600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>15700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>17200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>16600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>16300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>17200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>16000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>15700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>30200</v>
       </c>
-      <c r="M83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N83" s="3">
+      <c r="N83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O83" s="3">
         <v>51500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>-23000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>48800</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>8300</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>6800</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>10200</v>
       </c>
-      <c r="T83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U83" s="3" t="s">
         <v>3</v>
       </c>
@@ -5481,8 +5680,11 @@
       <c r="Y83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5552,8 +5754,11 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5623,8 +5828,11 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5694,8 +5902,11 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5765,8 +5976,11 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5836,62 +6050,65 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>33200</v>
+      </c>
+      <c r="E89" s="3">
         <v>63000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>27800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>17700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>30500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>109300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>28500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>68300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>34500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>102100</v>
       </c>
-      <c r="M89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N89" s="3">
+      <c r="N89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O89" s="3">
         <v>70400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>104400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-55600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>4900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-46200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-6000</v>
       </c>
-      <c r="T89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5907,8 +6124,11 @@
       <c r="Y89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5934,22 +6154,23 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>0</v>
+        <v>-500</v>
       </c>
       <c r="E91" s="3">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3">
         <v>-100</v>
       </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
       <c r="G91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="H91" s="3">
         <v>-100</v>
@@ -5958,7 +6179,7 @@
         <v>-100</v>
       </c>
       <c r="J91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
@@ -5966,30 +6187,30 @@
       <c r="L91" s="3">
         <v>0</v>
       </c>
-      <c r="M91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N91" s="3">
+      <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O91" s="3">
         <v>-100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-200</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-400</v>
       </c>
-      <c r="T91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U91" s="3" t="s">
         <v>3</v>
       </c>
@@ -6005,8 +6226,11 @@
       <c r="Y91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6076,8 +6300,11 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6147,62 +6374,65 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>0</v>
+        <v>-500</v>
       </c>
       <c r="E94" s="3">
+        <v>0</v>
+      </c>
+      <c r="F94" s="3">
         <v>-100</v>
       </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
       <c r="G94" s="3">
+        <v>0</v>
+      </c>
+      <c r="H94" s="3">
         <v>200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-100</v>
       </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
       <c r="J94" s="3">
+        <v>0</v>
+      </c>
+      <c r="K94" s="3">
         <v>47400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-46600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>200</v>
       </c>
-      <c r="M94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N94" s="3">
+      <c r="N94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O94" s="3">
         <v>-22600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-60800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>35200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-8900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>33200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-400</v>
       </c>
-      <c r="T94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U94" s="3" t="s">
         <v>3</v>
       </c>
@@ -6218,8 +6448,11 @@
       <c r="Y94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6245,32 +6478,33 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-600</v>
+        <v>0</v>
       </c>
       <c r="E96" s="3">
         <v>-600</v>
       </c>
       <c r="F96" s="3">
+        <v>-600</v>
+      </c>
+      <c r="G96" s="3">
         <v>-97400</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-16000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-8900</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-13700</v>
       </c>
-      <c r="J96" s="3">
-        <v>0</v>
-      </c>
       <c r="K96" s="3">
         <v>0</v>
       </c>
@@ -6316,8 +6550,11 @@
       <c r="Y96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6387,8 +6624,11 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6458,8 +6698,11 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6529,62 +6772,65 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-47000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-25700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-28000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-112600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-48900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-51900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-29700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-87300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>30500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-82300</v>
       </c>
-      <c r="M100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N100" s="3">
+      <c r="N100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O100" s="3">
         <v>-42000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-34600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>19400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>14700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>19500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-100</v>
       </c>
-      <c r="T100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6600,62 +6846,65 @@
       <c r="Y100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E101" s="3">
+        <v>0</v>
+      </c>
+      <c r="F101" s="3">
         <v>-200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>700</v>
-      </c>
-      <c r="G101" s="3">
-        <v>-1000</v>
       </c>
       <c r="H101" s="3">
         <v>-1000</v>
       </c>
       <c r="I101" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="J101" s="3">
         <v>600</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>100</v>
       </c>
-      <c r="M101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N101" s="3">
+      <c r="N101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O101" s="3">
         <v>-400</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-1200</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>100</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>2600</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-1300</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-300</v>
       </c>
-      <c r="T101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U101" s="3" t="s">
         <v>3</v>
       </c>
@@ -6671,62 +6920,65 @@
       <c r="Y101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-14300</v>
+      </c>
+      <c r="E102" s="3">
         <v>37200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-94300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-19200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>56400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>28100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>18000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>20100</v>
       </c>
-      <c r="M102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N102" s="3">
+      <c r="N102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O102" s="3">
         <v>5400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>7700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>13400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>5200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-6800</v>
       </c>
-      <c r="T102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U102" s="3" t="s">
         <v>3</v>
       </c>
@@ -6740,6 +6992,9 @@
         <v>3</v>
       </c>
       <c r="Y102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/GRIN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GRIN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="92">
   <si>
     <t>GRIN</t>
   </si>
@@ -656,97 +656,97 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Z102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="26" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="27" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44012</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>43830</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43646</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43281</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>42916</v>
       </c>
-      <c r="U7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V7" s="2" t="s">
         <v>3</v>
       </c>
@@ -762,65 +762,68 @@
       <c r="Z7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>88800</v>
+      </c>
+      <c r="E8" s="3">
         <v>112500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>109100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>76800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>81400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>107200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>161600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>110300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>89500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>135100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>178300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>68400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>112100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>167100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>163800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>167200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>150800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>194100</v>
       </c>
-      <c r="U8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V8" s="3" t="s">
         <v>3</v>
       </c>
@@ -836,65 +839,68 @@
       <c r="Z8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>77100</v>
+      </c>
+      <c r="E9" s="3">
         <v>108300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>92600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>69800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>58400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>68700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>97000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>69600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>22700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>73200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>132900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>55800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>105900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>158200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>149200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>161300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>148400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>184300</v>
       </c>
-      <c r="U9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V9" s="3" t="s">
         <v>3</v>
       </c>
@@ -910,65 +916,68 @@
       <c r="Z9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>11700</v>
+      </c>
+      <c r="E10" s="3">
         <v>4200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>16500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>7000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>23000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>38500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>64600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>40700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>66800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>61900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>45400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>12600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>6200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>8900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>14600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>5900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>2400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>9800</v>
       </c>
-      <c r="U10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V10" s="3" t="s">
         <v>3</v>
       </c>
@@ -984,8 +993,11 @@
       <c r="Z10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1012,8 +1024,9 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1086,8 +1099,11 @@
       <c r="Z12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1160,8 +1176,11 @@
       <c r="Z13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1198,17 +1217,17 @@
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P14" s="3">
         <v>14600</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>4200</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
-      <c r="R14" s="3" t="s">
-        <v>3</v>
+      <c r="R14" s="3">
+        <v>0</v>
       </c>
       <c r="S14" s="3" t="s">
         <v>3</v>
@@ -1225,8 +1244,8 @@
       <c r="W14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
+      <c r="X14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y14" s="3">
         <v>0</v>
@@ -1234,8 +1253,11 @@
       <c r="Z14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1272,18 +1294,18 @@
       <c r="N15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O15" s="3">
+      <c r="O15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P15" s="3">
         <v>600</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>400</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>600</v>
       </c>
-      <c r="R15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1296,8 +1318,8 @@
       <c r="V15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W15" s="3">
-        <v>0</v>
+      <c r="W15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X15" s="3">
         <v>0</v>
@@ -1308,8 +1330,11 @@
       <c r="Z15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1333,65 +1358,66 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-    </row>
-    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>90800</v>
+      </c>
+      <c r="E17" s="3">
         <v>120900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>103300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>81000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>85600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>85000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>104700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>81100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>31200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>85800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>147900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>65300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>140600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>179000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>188300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>185500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>162100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>199100</v>
       </c>
-      <c r="U17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1407,65 +1433,68 @@
       <c r="Z17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E18" s="3">
         <v>-8400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>5800</v>
-      </c>
-      <c r="F18" s="3">
-        <v>-4200</v>
       </c>
       <c r="G18" s="3">
         <v>-4200</v>
       </c>
       <c r="H18" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="I18" s="3">
         <v>22200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>56900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>29200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>58300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>49300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>30400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>3100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-28500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-11900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-24500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-18300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-11300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-5000</v>
       </c>
-      <c r="U18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1481,8 +1510,11 @@
       <c r="Z18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1509,8 +1541,9 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
-    </row>
-    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1565,8 +1598,8 @@
       <c r="T20" s="3">
         <v>0</v>
       </c>
-      <c r="U20" s="3" t="s">
-        <v>3</v>
+      <c r="U20" s="3">
+        <v>0</v>
       </c>
       <c r="V20" s="3" t="s">
         <v>3</v>
@@ -1583,65 +1616,68 @@
       <c r="Z20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>11300</v>
+      </c>
+      <c r="E21" s="3">
         <v>5600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>20400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>11500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>13000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>38800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>73200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>46400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>74200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>65100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>60600</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O21" s="3">
+      <c r="O21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P21" s="3">
         <v>23000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-34900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>24300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-10000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-4500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>5100</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1657,8 +1693,11 @@
       <c r="Z21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1731,65 +1770,68 @@
       <c r="Z22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-8400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>5800</v>
-      </c>
-      <c r="F23" s="3">
-        <v>-4200</v>
       </c>
       <c r="G23" s="3">
         <v>-4200</v>
       </c>
       <c r="H23" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="I23" s="3">
         <v>22200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>56900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>29200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>58200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>49300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>30400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>3200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-28500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-11900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-24500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-18300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-11300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-5100</v>
       </c>
-      <c r="U23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1805,65 +1847,68 @@
       <c r="Z23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="E24" s="3">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3">
         <v>200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>2300</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
-      </c>
       <c r="M24" s="3">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3">
         <v>-100</v>
       </c>
-      <c r="N24" s="3">
-        <v>0</v>
-      </c>
       <c r="O24" s="3">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3">
         <v>300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>2100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>1900</v>
       </c>
-      <c r="U24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1879,8 +1924,11 @@
       <c r="Z24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1953,65 +2001,68 @@
       <c r="Z25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E26" s="3">
         <v>-8500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>5500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-4300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-4600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>22200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>56800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>29000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>56000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>49300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>30400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>3200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-28800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-12300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-24500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-19000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-13500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-7000</v>
       </c>
-      <c r="U26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V26" s="3" t="s">
         <v>3</v>
       </c>
@@ -2027,65 +2078,68 @@
       <c r="Z26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E27" s="3">
         <v>-8500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>5500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-4300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-4600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>22200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>56800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>29000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>56000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>44200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>19900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>2200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-28300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-10500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-24500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-19000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-13500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-7000</v>
       </c>
-      <c r="U27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2101,8 +2155,11 @@
       <c r="Z27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2175,13 +2232,16 @@
       <c r="Z28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>3</v>
+      <c r="D29" s="3">
+        <v>0</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>3</v>
@@ -2189,41 +2249,41 @@
       <c r="F29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G29" s="3">
-        <v>0</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I29" s="3">
-        <v>0</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K29" s="3">
+      <c r="G29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J29" s="3">
+        <v>0</v>
+      </c>
+      <c r="K29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L29" s="3">
         <v>-3200</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>-200</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>-2800</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>200</v>
       </c>
-      <c r="O29" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P29" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R29" s="3">
-        <v>0</v>
+      <c r="R29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S29" s="3">
         <v>0</v>
@@ -2249,8 +2309,11 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2323,8 +2386,11 @@
       <c r="Z30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2397,8 +2463,11 @@
       <c r="Z31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2453,8 +2522,8 @@
       <c r="T32" s="3">
         <v>0</v>
       </c>
-      <c r="U32" s="3" t="s">
-        <v>3</v>
+      <c r="U32" s="3">
+        <v>0</v>
       </c>
       <c r="V32" s="3" t="s">
         <v>3</v>
@@ -2471,65 +2540,68 @@
       <c r="Z32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E33" s="3">
         <v>-8500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>5500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-4300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-4600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>22200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>56800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>29000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>52800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>44000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>17000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>2400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-28300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-10500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-24500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-19000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-13500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-7000</v>
       </c>
-      <c r="U33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2545,8 +2617,11 @@
       <c r="Z33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2619,65 +2694,68 @@
       <c r="Z34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E35" s="3">
         <v>-8500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>5500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-4300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-4600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>22200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>56800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>29000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>52800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>44000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>17000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>2400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-28300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-10500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-24500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-19000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-13500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-7000</v>
       </c>
-      <c r="U35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2693,70 +2771,73 @@
       <c r="Z35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44012</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>43830</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43646</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43281</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>42916</v>
       </c>
-      <c r="U38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2772,8 +2853,11 @@
       <c r="Z38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2800,8 +2884,9 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2828,62 +2913,63 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>59300</v>
+      </c>
+      <c r="E41" s="3">
         <v>71400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>85900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>51800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>52200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>146300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>165400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>106500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>107100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>78500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>60700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>41300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>44700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>35600</v>
-      </c>
-      <c r="Q41" s="3">
-        <v>37900</v>
       </c>
       <c r="R41" s="3">
         <v>37900</v>
       </c>
       <c r="S41" s="3">
+        <v>37900</v>
+      </c>
+      <c r="T41" s="3">
         <v>54100</v>
       </c>
-      <c r="T41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2893,17 +2979,20 @@
       <c r="W41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X41" s="3">
-        <v>0</v>
+      <c r="X41" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y41" s="3">
         <v>0</v>
       </c>
-      <c r="Z41" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="Z41" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2976,62 +3065,65 @@
       <c r="Z42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>27800</v>
+      </c>
+      <c r="E43" s="3">
         <v>24500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>24900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>28600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>37700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>37000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>41300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>38600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>35100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>34400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>31000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>28400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>39200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>38900</v>
-      </c>
-      <c r="Q43" s="3">
-        <v>45500</v>
       </c>
       <c r="R43" s="3">
         <v>45500</v>
       </c>
       <c r="S43" s="3">
+        <v>45500</v>
+      </c>
+      <c r="T43" s="3">
         <v>72700</v>
       </c>
-      <c r="T43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3041,71 +3133,74 @@
       <c r="W43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X43" s="3">
-        <v>0</v>
+      <c r="X43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y43" s="3">
         <v>0</v>
       </c>
-      <c r="Z43" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="Z43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>10800</v>
+      </c>
+      <c r="E44" s="3">
         <v>11500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>12500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>10900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>15300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>18100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>20100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>16800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>13900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>12600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>12700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>8700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>7800</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>12200</v>
-      </c>
-      <c r="Q44" s="3">
-        <v>8600</v>
       </c>
       <c r="R44" s="3">
         <v>8600</v>
       </c>
       <c r="S44" s="3">
+        <v>8600</v>
+      </c>
+      <c r="T44" s="3">
         <v>10900</v>
       </c>
-      <c r="T44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3115,71 +3210,74 @@
       <c r="W44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X44" s="3">
-        <v>0</v>
+      <c r="X44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y44" s="3">
         <v>0</v>
       </c>
-      <c r="Z44" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="Z44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>200</v>
+      </c>
+      <c r="E45" s="3">
         <v>400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>2400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>2700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>10600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>5400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>5800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>4300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>3800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>4900</v>
-      </c>
-      <c r="Q45" s="3">
-        <v>700</v>
       </c>
       <c r="R45" s="3">
         <v>700</v>
       </c>
       <c r="S45" s="3">
+        <v>700</v>
+      </c>
+      <c r="T45" s="3">
         <v>1100</v>
       </c>
-      <c r="T45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3189,71 +3287,74 @@
       <c r="W45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X45" s="3">
-        <v>0</v>
+      <c r="X45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y45" s="3">
         <v>0</v>
       </c>
-      <c r="Z45" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="Z45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>98100</v>
+      </c>
+      <c r="E46" s="3">
         <v>107700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>123400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>91500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>105200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>203700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>229400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>172500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>161500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>131300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>106800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>82600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>95600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>91500</v>
-      </c>
-      <c r="Q46" s="3">
-        <v>92700</v>
       </c>
       <c r="R46" s="3">
         <v>92700</v>
       </c>
       <c r="S46" s="3">
+        <v>92700</v>
+      </c>
+      <c r="T46" s="3">
         <v>138900</v>
       </c>
-      <c r="T46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3263,71 +3364,74 @@
       <c r="W46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X46" s="3">
-        <v>0</v>
+      <c r="X46" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y46" s="3">
         <v>0</v>
       </c>
-      <c r="Z46" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="Z46" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>5500</v>
+      </c>
+      <c r="E47" s="3">
         <v>5200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>6500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>6400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>4600</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>5500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>5000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>5500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>4100</v>
-      </c>
-      <c r="L47" s="3">
-        <v>3200</v>
       </c>
       <c r="M47" s="3">
         <v>3200</v>
       </c>
       <c r="N47" s="3">
+        <v>3200</v>
+      </c>
+      <c r="O47" s="3">
         <v>3300</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>3900</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>55100</v>
-      </c>
-      <c r="Q47" s="3">
-        <v>52100</v>
       </c>
       <c r="R47" s="3">
         <v>52100</v>
       </c>
       <c r="S47" s="3">
+        <v>52100</v>
+      </c>
+      <c r="T47" s="3">
         <v>65300</v>
       </c>
-      <c r="T47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3337,71 +3441,74 @@
       <c r="W47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X47" s="3">
-        <v>0</v>
+      <c r="X47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y47" s="3">
         <v>0</v>
       </c>
-      <c r="Z47" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="Z47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>338400</v>
+      </c>
+      <c r="E48" s="3">
         <v>353400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>373200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>406700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>433600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>436200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>443800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>470100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>469900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>483600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>465900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>524400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>538600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>360400</v>
-      </c>
-      <c r="Q48" s="3">
-        <v>355400</v>
       </c>
       <c r="R48" s="3">
         <v>355400</v>
       </c>
       <c r="S48" s="3">
+        <v>355400</v>
+      </c>
+      <c r="T48" s="3">
         <v>262400</v>
       </c>
-      <c r="T48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3411,25 +3518,28 @@
       <c r="W48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X48" s="3">
-        <v>0</v>
+      <c r="X48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y48" s="3">
         <v>0</v>
       </c>
-      <c r="Z48" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="Z48" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>12800</v>
+      </c>
+      <c r="E49" s="3">
         <v>100</v>
-      </c>
-      <c r="E49" s="3">
-        <v>200</v>
       </c>
       <c r="F49" s="3">
         <v>200</v>
@@ -3450,32 +3560,32 @@
         <v>200</v>
       </c>
       <c r="L49" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="M49" s="3">
         <v>300</v>
       </c>
       <c r="N49" s="3">
+        <v>300</v>
+      </c>
+      <c r="O49" s="3">
         <v>1400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1100</v>
-      </c>
-      <c r="Q49" s="3">
-        <v>7600</v>
       </c>
       <c r="R49" s="3">
         <v>7600</v>
       </c>
       <c r="S49" s="3">
+        <v>7600</v>
+      </c>
+      <c r="T49" s="3">
         <v>7700</v>
       </c>
-      <c r="T49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3485,17 +3595,20 @@
       <c r="W49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X49" s="3">
-        <v>0</v>
+      <c r="X49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y49" s="3">
         <v>0</v>
       </c>
-      <c r="Z49" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="Z49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3568,8 +3681,11 @@
       <c r="Z50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3642,62 +3758,65 @@
       <c r="Z51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>5400</v>
+        <v>6000</v>
       </c>
       <c r="E52" s="3">
         <v>5400</v>
       </c>
       <c r="F52" s="3">
-        <v>5600</v>
+        <v>5400</v>
       </c>
       <c r="G52" s="3">
         <v>5600</v>
       </c>
       <c r="H52" s="3">
+        <v>5600</v>
+      </c>
+      <c r="I52" s="3">
         <v>6000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>6400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>8300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>9400</v>
-      </c>
-      <c r="L52" s="3">
-        <v>8600</v>
       </c>
       <c r="M52" s="3">
         <v>8600</v>
       </c>
       <c r="N52" s="3">
+        <v>8600</v>
+      </c>
+      <c r="O52" s="3">
         <v>10400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>11700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>10900</v>
-      </c>
-      <c r="Q52" s="3">
-        <v>14200</v>
       </c>
       <c r="R52" s="3">
         <v>14200</v>
       </c>
       <c r="S52" s="3">
+        <v>14200</v>
+      </c>
+      <c r="T52" s="3">
         <v>1000</v>
       </c>
-      <c r="T52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3707,17 +3826,20 @@
       <c r="W52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X52" s="3">
-        <v>0</v>
+      <c r="X52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y52" s="3">
         <v>0</v>
       </c>
-      <c r="Z52" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="Z52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3790,62 +3912,65 @@
       <c r="Z53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>460900</v>
+      </c>
+      <c r="E54" s="3">
         <v>471800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>508700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>510400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>549200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>651700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>684800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>656700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>645200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>627000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>584900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>622100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>651000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>519100</v>
-      </c>
-      <c r="Q54" s="3">
-        <v>521900</v>
       </c>
       <c r="R54" s="3">
         <v>521900</v>
       </c>
       <c r="S54" s="3">
+        <v>521900</v>
+      </c>
+      <c r="T54" s="3">
         <v>475300</v>
       </c>
-      <c r="T54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3855,17 +3980,20 @@
       <c r="W54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X54" s="3">
-        <v>0</v>
+      <c r="X54" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y54" s="3">
         <v>0</v>
       </c>
-      <c r="Z54" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="Z54" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3892,8 +4020,9 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3920,62 +4049,63 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>30700</v>
+      </c>
+      <c r="E57" s="3">
         <v>17600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>15000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>17700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>29600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>28000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>27700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>24400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>33900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>31500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>29200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>27400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>24100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>28300</v>
-      </c>
-      <c r="Q57" s="3">
-        <v>27200</v>
       </c>
       <c r="R57" s="3">
         <v>27200</v>
       </c>
       <c r="S57" s="3">
+        <v>27200</v>
+      </c>
+      <c r="T57" s="3">
         <v>20400</v>
       </c>
-      <c r="T57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3985,71 +4115,74 @@
       <c r="W57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X57" s="3">
-        <v>0</v>
+      <c r="X57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y57" s="3">
         <v>0</v>
       </c>
-      <c r="Z57" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="Z57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>51000</v>
+      </c>
+      <c r="E58" s="3">
         <v>39100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>56500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>48500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>55400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>55700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>76600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>65900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>55400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>60200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>55700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>81500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>101600</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>45000</v>
-      </c>
-      <c r="Q58" s="3">
-        <v>46100</v>
       </c>
       <c r="R58" s="3">
         <v>46100</v>
       </c>
       <c r="S58" s="3">
+        <v>46100</v>
+      </c>
+      <c r="T58" s="3">
         <v>19200</v>
       </c>
-      <c r="T58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4059,71 +4192,74 @@
       <c r="W58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X58" s="3">
-        <v>0</v>
+      <c r="X58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y58" s="3">
         <v>0</v>
       </c>
-      <c r="Z58" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="Z58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E59" s="3">
         <v>4400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>3900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>4000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>5700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>6900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>15000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>7400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>11100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>10100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>13300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>9000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>9400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>13500</v>
-      </c>
-      <c r="Q59" s="3">
-        <v>15400</v>
       </c>
       <c r="R59" s="3">
         <v>15400</v>
       </c>
       <c r="S59" s="3">
+        <v>15400</v>
+      </c>
+      <c r="T59" s="3">
         <v>22800</v>
       </c>
-      <c r="T59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4133,71 +4269,74 @@
       <c r="W59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X59" s="3">
-        <v>0</v>
+      <c r="X59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y59" s="3">
         <v>0</v>
       </c>
-      <c r="Z59" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="Z59" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>86600</v>
+      </c>
+      <c r="E60" s="3">
         <v>61100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>75400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>70300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>90700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>90600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>119300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>97700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>100300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>101800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>98100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>117900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>135100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>86800</v>
-      </c>
-      <c r="Q60" s="3">
-        <v>88700</v>
       </c>
       <c r="R60" s="3">
         <v>88700</v>
       </c>
       <c r="S60" s="3">
+        <v>88700</v>
+      </c>
+      <c r="T60" s="3">
         <v>62400</v>
       </c>
-      <c r="T60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4207,71 +4346,74 @@
       <c r="W60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X60" s="3">
-        <v>0</v>
+      <c r="X60" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y60" s="3">
         <v>0</v>
       </c>
-      <c r="Z60" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="Z60" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>125000</v>
+      </c>
+      <c r="E61" s="3">
         <v>129800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>144400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>156200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>169700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>170100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>176200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>214800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>223500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>234000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>200600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>248200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>238300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>178200</v>
-      </c>
-      <c r="Q61" s="3">
-        <v>154200</v>
       </c>
       <c r="R61" s="3">
         <v>154200</v>
       </c>
       <c r="S61" s="3">
+        <v>154200</v>
+      </c>
+      <c r="T61" s="3">
         <v>108100</v>
       </c>
-      <c r="T61" s="3">
-        <v>0</v>
-      </c>
       <c r="U61" s="3">
         <v>0</v>
       </c>
@@ -4290,62 +4432,65 @@
       <c r="Z61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1100</v>
+        <v>3100</v>
       </c>
       <c r="E62" s="3">
         <v>1100</v>
       </c>
       <c r="F62" s="3">
+        <v>1100</v>
+      </c>
+      <c r="G62" s="3">
         <v>1200</v>
-      </c>
-      <c r="G62" s="3">
-        <v>1400</v>
       </c>
       <c r="H62" s="3">
         <v>1400</v>
       </c>
       <c r="I62" s="3">
+        <v>1400</v>
+      </c>
+      <c r="J62" s="3">
         <v>1800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>2100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2300</v>
-      </c>
-      <c r="M62" s="3">
-        <v>2000</v>
       </c>
       <c r="N62" s="3">
         <v>2000</v>
       </c>
       <c r="O62" s="3">
+        <v>2000</v>
+      </c>
+      <c r="P62" s="3">
         <v>1700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>2100</v>
-      </c>
-      <c r="Q62" s="3">
-        <v>2300</v>
       </c>
       <c r="R62" s="3">
         <v>2300</v>
       </c>
       <c r="S62" s="3">
+        <v>2300</v>
+      </c>
+      <c r="T62" s="3">
         <v>2500</v>
       </c>
-      <c r="T62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4355,17 +4500,20 @@
       <c r="W62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X62" s="3">
-        <v>0</v>
+      <c r="X62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y62" s="3">
         <v>0</v>
       </c>
-      <c r="Z62" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="Z62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4438,8 +4586,11 @@
       <c r="Z63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4512,8 +4663,11 @@
       <c r="Z64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4586,62 +4740,65 @@
       <c r="Z65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>214800</v>
+      </c>
+      <c r="E66" s="3">
         <v>192000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>220900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>227700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>261800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>262100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>297400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>314500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>325500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>338100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>347900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>409900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>417400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>267100</v>
-      </c>
-      <c r="Q66" s="3">
-        <v>245200</v>
       </c>
       <c r="R66" s="3">
         <v>245200</v>
       </c>
       <c r="S66" s="3">
+        <v>245200</v>
+      </c>
+      <c r="T66" s="3">
         <v>172900</v>
       </c>
-      <c r="T66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4651,17 +4808,20 @@
       <c r="W66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X66" s="3">
-        <v>0</v>
+      <c r="X66" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y66" s="3">
         <v>0</v>
       </c>
-      <c r="Z66" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="Z66" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4688,8 +4848,9 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
-    </row>
-    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4762,8 +4923,11 @@
       <c r="Z68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4836,8 +5000,11 @@
       <c r="Z69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4910,8 +5077,11 @@
       <c r="Z70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4984,62 +5154,65 @@
       <c r="Z71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-32200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-40900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-32900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-38000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-21200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>68800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>73100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>21500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>15100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-31700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-77500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-99800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-75500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-64400</v>
-      </c>
-      <c r="Q72" s="3">
-        <v>-43900</v>
       </c>
       <c r="R72" s="3">
         <v>-43900</v>
       </c>
       <c r="S72" s="3">
+        <v>-43900</v>
+      </c>
+      <c r="T72" s="3">
         <v>-19600</v>
       </c>
-      <c r="T72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5049,17 +5222,20 @@
       <c r="W72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X72" s="3">
-        <v>0</v>
+      <c r="X72" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y72" s="3">
         <v>0</v>
       </c>
-      <c r="Z72" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="Z72" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5132,8 +5308,11 @@
       <c r="Z73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5206,8 +5385,11 @@
       <c r="Z74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5280,62 +5462,65 @@
       <c r="Z75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>246100</v>
+      </c>
+      <c r="E76" s="3">
         <v>279800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>287800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>282700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>287400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>389500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>387500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>342100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>319600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>289000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>236900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>212200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>233600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>251900</v>
-      </c>
-      <c r="Q76" s="3">
-        <v>276700</v>
       </c>
       <c r="R76" s="3">
         <v>276700</v>
       </c>
       <c r="S76" s="3">
+        <v>276700</v>
+      </c>
+      <c r="T76" s="3">
         <v>302400</v>
       </c>
-      <c r="T76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5345,17 +5530,20 @@
       <c r="W76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X76" s="3">
-        <v>0</v>
+      <c r="X76" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y76" s="3">
         <v>0</v>
       </c>
-      <c r="Z76" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="Z76" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5428,70 +5616,73 @@
       <c r="Z77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44012</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>43830</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43646</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43281</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>42916</v>
       </c>
-      <c r="U80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V80" s="2" t="s">
         <v>3</v>
       </c>
@@ -5507,65 +5698,68 @@
       <c r="Z80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E81" s="3">
         <v>-8500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>5500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-4300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-4600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>22200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>56800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>29000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>52800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>44000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>17000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>2400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-28300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-10500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-24500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-19000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-13500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-7000</v>
       </c>
-      <c r="U81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V81" s="3" t="s">
         <v>3</v>
       </c>
@@ -5581,8 +5775,11 @@
       <c r="Z81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5609,65 +5806,66 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
-    </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>13300</v>
+      </c>
+      <c r="E83" s="3">
         <v>14000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>14600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>15700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>17200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>16600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>16300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>17200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>16000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>15700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>30200</v>
       </c>
-      <c r="N83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O83" s="3">
+      <c r="O83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P83" s="3">
         <v>51500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>-23000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>48800</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>8300</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>6800</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>10200</v>
       </c>
-      <c r="U83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V83" s="3" t="s">
         <v>3</v>
       </c>
@@ -5683,8 +5881,11 @@
       <c r="Z83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5757,8 +5958,11 @@
       <c r="Z84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5831,8 +6035,11 @@
       <c r="Z85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5905,8 +6112,11 @@
       <c r="Z86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5979,8 +6189,11 @@
       <c r="Z87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6053,65 +6266,68 @@
       <c r="Z88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>31100</v>
+      </c>
+      <c r="E89" s="3">
         <v>33200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>63000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>27800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>17700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>30500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>109300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>28500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>68300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>34500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>102100</v>
       </c>
-      <c r="N89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O89" s="3">
+      <c r="O89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P89" s="3">
         <v>70400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>104400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-55600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>4900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-46200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-6000</v>
       </c>
-      <c r="U89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V89" s="3" t="s">
         <v>3</v>
       </c>
@@ -6127,8 +6343,11 @@
       <c r="Z89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6155,25 +6374,26 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
-    </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-500</v>
       </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
       <c r="F91" s="3">
+        <v>0</v>
+      </c>
+      <c r="G91" s="3">
         <v>-100</v>
       </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
       <c r="H91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="I91" s="3">
         <v>-100</v>
@@ -6182,7 +6402,7 @@
         <v>-100</v>
       </c>
       <c r="K91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="L91" s="3">
         <v>0</v>
@@ -6190,30 +6410,30 @@
       <c r="M91" s="3">
         <v>0</v>
       </c>
-      <c r="N91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O91" s="3">
+      <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P91" s="3">
         <v>-100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-200</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-400</v>
       </c>
-      <c r="U91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V91" s="3" t="s">
         <v>3</v>
       </c>
@@ -6229,8 +6449,11 @@
       <c r="Z91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6303,8 +6526,11 @@
       <c r="Z92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6377,65 +6603,68 @@
       <c r="Z93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-500</v>
       </c>
-      <c r="E94" s="3">
-        <v>0</v>
-      </c>
       <c r="F94" s="3">
+        <v>0</v>
+      </c>
+      <c r="G94" s="3">
         <v>-100</v>
       </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
       <c r="H94" s="3">
+        <v>0</v>
+      </c>
+      <c r="I94" s="3">
         <v>200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-100</v>
       </c>
-      <c r="J94" s="3">
-        <v>0</v>
-      </c>
       <c r="K94" s="3">
+        <v>0</v>
+      </c>
+      <c r="L94" s="3">
         <v>47400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-46600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>200</v>
       </c>
-      <c r="N94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O94" s="3">
+      <c r="O94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P94" s="3">
         <v>-22600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-60800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>35200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-8900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>33200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-400</v>
       </c>
-      <c r="U94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V94" s="3" t="s">
         <v>3</v>
       </c>
@@ -6451,8 +6680,11 @@
       <c r="Z94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6479,8 +6711,9 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
-    </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6488,26 +6721,26 @@
         <v>0</v>
       </c>
       <c r="E96" s="3">
-        <v>-600</v>
+        <v>0</v>
       </c>
       <c r="F96" s="3">
         <v>-600</v>
       </c>
       <c r="G96" s="3">
+        <v>-600</v>
+      </c>
+      <c r="H96" s="3">
         <v>-97400</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-16000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-8900</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-13700</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
       <c r="L96" s="3">
         <v>0</v>
       </c>
@@ -6553,8 +6786,11 @@
       <c r="Z96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6627,8 +6863,11 @@
       <c r="Z97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6701,8 +6940,11 @@
       <c r="Z98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6775,65 +7017,68 @@
       <c r="Z99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-46800</v>
+      </c>
+      <c r="E100" s="3">
         <v>-47000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-25700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-28000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-112600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-48900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-51900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-29700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-87300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>30500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-82300</v>
       </c>
-      <c r="N100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O100" s="3">
+      <c r="O100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P100" s="3">
         <v>-42000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-34600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>19400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>14700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>19500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-100</v>
       </c>
-      <c r="U100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6849,65 +7094,68 @@
       <c r="Z100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>100</v>
+      </c>
+      <c r="E101" s="3">
         <v>-100</v>
       </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
       <c r="F101" s="3">
+        <v>0</v>
+      </c>
+      <c r="G101" s="3">
         <v>-200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>700</v>
-      </c>
-      <c r="H101" s="3">
-        <v>-1000</v>
       </c>
       <c r="I101" s="3">
         <v>-1000</v>
       </c>
       <c r="J101" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="K101" s="3">
         <v>600</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>100</v>
       </c>
-      <c r="N101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O101" s="3">
+      <c r="O101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P101" s="3">
         <v>-400</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>100</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>2600</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-1300</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-300</v>
       </c>
-      <c r="U101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V101" s="3" t="s">
         <v>3</v>
       </c>
@@ -6923,65 +7171,68 @@
       <c r="Z101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-13800</v>
+      </c>
+      <c r="E102" s="3">
         <v>-14300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>37200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-94300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-19200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>56400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>28100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>18000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>20100</v>
       </c>
-      <c r="N102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O102" s="3">
+      <c r="O102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P102" s="3">
         <v>5400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>7700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-1000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>13400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>5200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-6800</v>
       </c>
-      <c r="U102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V102" s="3" t="s">
         <v>3</v>
       </c>
@@ -6995,6 +7246,9 @@
         <v>3</v>
       </c>
       <c r="Z102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
